--- a/report_show.xlsx
+++ b/report_show.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30051045\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\笔记\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9CE6E10-B08B-4E58-AB27-D9CC95AB42A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74667AFE-1DAE-47E3-BC6E-9A225F8930AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="行动计划及执行情况确认表" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
   <si>
     <t>人事</t>
   </si>
@@ -153,7 +153,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -179,7 +179,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -373,6 +373,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -403,25 +421,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -435,7 +435,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1480,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Q15"/>
+  <dimension ref="B2:Q60"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
@@ -1500,226 +1500,456 @@
       </c>
     </row>
     <row r="3" spans="2:17">
-      <c r="P3" s="9"/>
-      <c r="Q3" s="10"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="P4" s="9"/>
-      <c r="Q4" s="11"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="P5" s="9"/>
-      <c r="Q5" s="12"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="18"/>
     </row>
     <row r="6" spans="2:17">
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="2:17" ht="26" customHeight="1">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
     </row>
     <row r="8" spans="2:17" ht="26" customHeight="1">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="21"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="2:17" ht="128" customHeight="1">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="15"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="21"/>
     </row>
     <row r="10" spans="2:17" ht="17" customHeight="1">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="8"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="2:17" ht="26" customHeight="1">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="2:17" ht="26" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
     </row>
     <row r="13" spans="2:17" ht="58" customHeight="1">
       <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="2:17" ht="60" customHeight="1">
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
     </row>
     <row r="15" spans="2:17" ht="59.5" customHeight="1">
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+    </row>
+    <row r="47" spans="16:17">
+      <c r="P47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="16:17">
+      <c r="P48" s="15"/>
+      <c r="Q48" s="16"/>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="P49" s="15"/>
+      <c r="Q49" s="17"/>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="P50" s="15"/>
+      <c r="Q50" s="18"/>
+    </row>
+    <row r="51" spans="2:17">
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+    </row>
+    <row r="52" spans="2:17" ht="26" customHeight="1">
+      <c r="B52" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
+    </row>
+    <row r="53" spans="2:17" ht="26" customHeight="1">
+      <c r="B53" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="8"/>
+    </row>
+    <row r="54" spans="2:17" ht="128" customHeight="1">
+      <c r="B54" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="21"/>
+    </row>
+    <row r="55" spans="2:17" ht="17" customHeight="1">
+      <c r="B55" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="14"/>
+    </row>
+    <row r="56" spans="2:17" ht="26" customHeight="1">
+      <c r="B56" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+    </row>
+    <row r="57" spans="2:17" ht="26" customHeight="1">
+      <c r="B57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+    </row>
+    <row r="58" spans="2:17" ht="58" customHeight="1">
+      <c r="B58" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="10"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
+    </row>
+    <row r="59" spans="2:17" ht="60" customHeight="1">
+      <c r="B59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9"/>
+    </row>
+    <row r="60" spans="2:17" ht="59.5" customHeight="1">
+      <c r="B60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="M13:Q13"/>
+  <mergeCells count="42">
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="H60:L60"/>
+    <mergeCell ref="M60:Q60"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="H58:L58"/>
+    <mergeCell ref="M58:Q58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H59:L59"/>
+    <mergeCell ref="M59:Q59"/>
+    <mergeCell ref="B54:Q54"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H56:Q56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="H57:L57"/>
+    <mergeCell ref="M57:Q57"/>
+    <mergeCell ref="P48:P50"/>
+    <mergeCell ref="Q48:Q50"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="N53:Q53"/>
     <mergeCell ref="B10:Q10"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="Q3:Q5"/>
@@ -1732,9 +1962,22 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="H11:Q11"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="M13:Q13"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -1760,106 +2003,106 @@
       </c>
     </row>
     <row r="6" spans="2:17">
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
     </row>
     <row r="7" spans="2:17">
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
     </row>
     <row r="8" spans="2:17">
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
     </row>
     <row r="9" spans="2:17">
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="2:17" ht="26" customHeight="1">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
     </row>
     <row r="11" spans="2:17" ht="26" customHeight="1">
       <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
       <c r="M11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="21"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="8"/>
     </row>
     <row r="12" spans="2:17" ht="128" customHeight="1">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="15"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="21"/>
     </row>
     <row r="13" spans="2:17" ht="17" customHeight="1">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:17" ht="26" customHeight="1">
       <c r="B14" s="23" t="s">
@@ -1887,302 +2130,270 @@
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22" t="s">
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="22"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="22"/>
-      <c r="Q15" s="22"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
     </row>
     <row r="16" spans="2:17" ht="35.5" customHeight="1">
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
     </row>
     <row r="17" spans="2:17" ht="35.5" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
     </row>
     <row r="18" spans="2:17" ht="35.5" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
     </row>
     <row r="19" spans="2:17" ht="35.5" customHeight="1">
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="2:17" ht="35.5" customHeight="1">
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="2:17" ht="35.5" customHeight="1">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
     </row>
     <row r="22" spans="2:17" ht="35.5" customHeight="1">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="2:17" ht="35.5" customHeight="1">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
     </row>
     <row r="24" spans="2:17" ht="35.5" customHeight="1">
       <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
     </row>
     <row r="25" spans="2:17" ht="35.5" customHeight="1">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
     </row>
     <row r="26" spans="2:17" ht="35.5" customHeight="1">
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
     </row>
     <row r="27" spans="2:17" ht="35.5" customHeight="1">
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B13:Q13"/>
-    <mergeCell ref="B12:Q12"/>
-    <mergeCell ref="B10:Q10"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="H14:Q14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:L22"/>
-    <mergeCell ref="M22:Q22"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="M27:Q27"/>
@@ -2199,9 +2410,47 @@
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="H24:L24"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:Q14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="B13:Q13"/>
+    <mergeCell ref="B12:Q12"/>
+    <mergeCell ref="B10:Q10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="N11:Q11"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{5db29ff9-328f-40bc-bdc5-3c7b0421d507}" enabled="1" method="Standard" siteId="{0da2a83b-13d9-4a35-965f-ec53a220ed9d}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/report_show.xlsx
+++ b/report_show.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\笔记\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74667AFE-1DAE-47E3-BC6E-9A225F8930AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299D9AD1-6B0D-4FDE-9E79-521F9E05DEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -373,6 +373,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -382,14 +388,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -399,6 +405,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -411,15 +420,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1500,16 +1500,16 @@
       </c>
     </row>
     <row r="3" spans="2:17">
-      <c r="P3" s="15"/>
-      <c r="Q3" s="16"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="19"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="P4" s="15"/>
-      <c r="Q4" s="17"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="P5" s="15"/>
-      <c r="Q5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="21"/>
     </row>
     <row r="6" spans="2:17">
       <c r="P6" s="5"/>
@@ -1539,175 +1539,175 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
       <c r="M8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="8"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" spans="2:17" ht="128" customHeight="1">
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="21"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="13"/>
     </row>
     <row r="10" spans="2:17" ht="17" customHeight="1">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="2:17" ht="26" customHeight="1">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11" t="s">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="2:17" ht="26" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11" t="s">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
     </row>
     <row r="13" spans="2:17" ht="58" customHeight="1">
       <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="2:17" ht="60" customHeight="1">
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
     </row>
     <row r="15" spans="2:17" ht="59.5" customHeight="1">
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="Q15" s="9"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
     </row>
     <row r="47" spans="16:17">
       <c r="P47" s="4" t="s">
@@ -1718,16 +1718,16 @@
       </c>
     </row>
     <row r="48" spans="16:17">
-      <c r="P48" s="15"/>
-      <c r="Q48" s="16"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="19"/>
     </row>
     <row r="49" spans="2:17">
-      <c r="P49" s="15"/>
-      <c r="Q49" s="17"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="20"/>
     </row>
     <row r="50" spans="2:17">
-      <c r="P50" s="15"/>
-      <c r="Q50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="21"/>
     </row>
     <row r="51" spans="2:17">
       <c r="P51" s="5"/>
@@ -1757,199 +1757,187 @@
       <c r="B53" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
       <c r="M53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N53" s="6" t="s">
+      <c r="N53" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="O53" s="7"/>
-      <c r="P53" s="7"/>
-      <c r="Q53" s="8"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="10"/>
     </row>
     <row r="54" spans="2:17" ht="128" customHeight="1">
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="21"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="13"/>
     </row>
     <row r="55" spans="2:17" ht="17" customHeight="1">
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="13"/>
-      <c r="Q55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="16"/>
     </row>
     <row r="56" spans="2:17" ht="26" customHeight="1">
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11" t="s">
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="11"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="17"/>
+      <c r="P56" s="17"/>
+      <c r="Q56" s="17"/>
     </row>
     <row r="57" spans="2:17" ht="26" customHeight="1">
       <c r="B57" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11" t="s">
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11" t="s">
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
-      <c r="Q57" s="11"/>
+      <c r="N57" s="17"/>
+      <c r="O57" s="17"/>
+      <c r="P57" s="17"/>
+      <c r="Q57" s="17"/>
     </row>
     <row r="58" spans="2:17" ht="58" customHeight="1">
       <c r="B58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
-      <c r="O58" s="9"/>
-      <c r="P58" s="9"/>
-      <c r="Q58" s="9"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
+      <c r="L58" s="7"/>
+      <c r="M58" s="7"/>
+      <c r="N58" s="7"/>
+      <c r="O58" s="7"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="2:17" ht="60" customHeight="1">
       <c r="B59" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-      <c r="O59" s="9"/>
-      <c r="P59" s="9"/>
-      <c r="Q59" s="9"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
     </row>
     <row r="60" spans="2:17" ht="59.5" customHeight="1">
       <c r="B60" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
-      <c r="O60" s="9"/>
-      <c r="P60" s="9"/>
-      <c r="Q60" s="9"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="H60:L60"/>
-    <mergeCell ref="M60:Q60"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="H58:L58"/>
-    <mergeCell ref="M58:Q58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H59:L59"/>
-    <mergeCell ref="M59:Q59"/>
-    <mergeCell ref="B54:Q54"/>
-    <mergeCell ref="B55:Q55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H56:Q56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="H57:L57"/>
-    <mergeCell ref="M57:Q57"/>
-    <mergeCell ref="P48:P50"/>
-    <mergeCell ref="Q48:Q50"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="N53:Q53"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="M13:Q13"/>
     <mergeCell ref="B10:Q10"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="Q3:Q5"/>
@@ -1962,15 +1950,27 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="H11:Q11"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="P48:P50"/>
+    <mergeCell ref="Q48:Q50"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="N53:Q53"/>
+    <mergeCell ref="B54:Q54"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H56:Q56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="H57:L57"/>
+    <mergeCell ref="M57:Q57"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="H60:L60"/>
+    <mergeCell ref="M60:Q60"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="H58:L58"/>
+    <mergeCell ref="M58:Q58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H59:L59"/>
+    <mergeCell ref="M59:Q59"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2003,16 +2003,16 @@
       </c>
     </row>
     <row r="6" spans="2:17">
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
     </row>
     <row r="7" spans="2:17">
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
     </row>
     <row r="8" spans="2:17">
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
     </row>
     <row r="9" spans="2:17">
       <c r="P9" s="5"/>
@@ -2042,67 +2042,67 @@
       <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
       <c r="M11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" spans="2:17" ht="128" customHeight="1">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="21"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="13"/>
     </row>
     <row r="13" spans="2:17" ht="17" customHeight="1">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="16"/>
     </row>
     <row r="14" spans="2:17" ht="26" customHeight="1">
       <c r="B14" s="23" t="s">
@@ -2130,270 +2130,302 @@
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11" t="s">
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="2:17" ht="35.5" customHeight="1">
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="2:17" ht="35.5" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
     </row>
     <row r="18" spans="2:17" ht="35.5" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
     </row>
     <row r="19" spans="2:17" ht="35.5" customHeight="1">
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="2:17" ht="35.5" customHeight="1">
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
     </row>
     <row r="21" spans="2:17" ht="35.5" customHeight="1">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="9"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="2:17" ht="35.5" customHeight="1">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
     </row>
     <row r="23" spans="2:17" ht="35.5" customHeight="1">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
     </row>
     <row r="24" spans="2:17" ht="35.5" customHeight="1">
       <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
     </row>
     <row r="25" spans="2:17" ht="35.5" customHeight="1">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
     </row>
     <row r="26" spans="2:17" ht="35.5" customHeight="1">
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
     </row>
     <row r="27" spans="2:17" ht="35.5" customHeight="1">
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="B13:Q13"/>
+    <mergeCell ref="B12:Q12"/>
+    <mergeCell ref="B10:Q10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:Q14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="M22:Q22"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="M27:Q27"/>
@@ -2410,38 +2442,6 @@
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="H24:L24"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:L22"/>
-    <mergeCell ref="M22:Q22"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="H14:Q14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="B13:Q13"/>
-    <mergeCell ref="B12:Q12"/>
-    <mergeCell ref="B10:Q10"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="N11:Q11"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report_show.xlsx
+++ b/report_show.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\笔记\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299D9AD1-6B0D-4FDE-9E79-521F9E05DEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCEA168-87EC-4F6B-A8E5-54B19D3F42E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>人事</t>
   </si>
@@ -142,6 +142,10 @@
   </si>
   <si>
     <t>2025/7/11</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>2026/5/21</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -373,12 +377,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -388,14 +386,14 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -405,9 +403,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -420,6 +415,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1500,16 +1504,16 @@
       </c>
     </row>
     <row r="3" spans="2:17">
-      <c r="P3" s="18"/>
-      <c r="Q3" s="19"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="16"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="P4" s="18"/>
-      <c r="Q4" s="20"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" spans="2:17">
-      <c r="P5" s="18"/>
-      <c r="Q5" s="21"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="18"/>
     </row>
     <row r="6" spans="2:17">
       <c r="P6" s="5"/>
@@ -1539,175 +1543,175 @@
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="10"/>
+      <c r="N8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="8"/>
     </row>
     <row r="9" spans="2:17" ht="128" customHeight="1">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="13"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="21"/>
     </row>
     <row r="10" spans="2:17" ht="17" customHeight="1">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="16"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="2:17" ht="26" customHeight="1">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="2:17" ht="26" customHeight="1">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
     </row>
     <row r="13" spans="2:17" ht="58" customHeight="1">
       <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
     </row>
     <row r="14" spans="2:17" ht="60" customHeight="1">
       <c r="B14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
     </row>
     <row r="15" spans="2:17" ht="59.5" customHeight="1">
       <c r="B15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
     </row>
     <row r="47" spans="16:17">
       <c r="P47" s="4" t="s">
@@ -1718,16 +1722,16 @@
       </c>
     </row>
     <row r="48" spans="16:17">
-      <c r="P48" s="18"/>
-      <c r="Q48" s="19"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="16"/>
     </row>
     <row r="49" spans="2:17">
-      <c r="P49" s="18"/>
-      <c r="Q49" s="20"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="17"/>
     </row>
     <row r="50" spans="2:17">
-      <c r="P50" s="18"/>
-      <c r="Q50" s="21"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="18"/>
     </row>
     <row r="51" spans="2:17">
       <c r="P51" s="5"/>
@@ -1757,187 +1761,199 @@
       <c r="B53" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
       <c r="M53" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N53" s="8" t="s">
+      <c r="N53" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="10"/>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="8"/>
     </row>
     <row r="54" spans="2:17" ht="128" customHeight="1">
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="12"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="12"/>
-      <c r="P54" s="12"/>
-      <c r="Q54" s="13"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="21"/>
     </row>
     <row r="55" spans="2:17" ht="17" customHeight="1">
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="16"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="14"/>
     </row>
     <row r="56" spans="2:17" ht="26" customHeight="1">
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="17" t="s">
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I56" s="17"/>
-      <c r="J56" s="17"/>
-      <c r="K56" s="17"/>
-      <c r="L56" s="17"/>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17"/>
-      <c r="O56" s="17"/>
-      <c r="P56" s="17"/>
-      <c r="Q56" s="17"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
     </row>
     <row r="57" spans="2:17" ht="26" customHeight="1">
       <c r="B57" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="17" t="s">
+      <c r="C57" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="17" t="s">
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I57" s="17"/>
-      <c r="J57" s="17"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="17" t="s">
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
-      <c r="P57" s="17"/>
-      <c r="Q57" s="17"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
     </row>
     <row r="58" spans="2:17" ht="58" customHeight="1">
       <c r="B58" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="7"/>
-      <c r="O58" s="7"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="7"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9"/>
     </row>
     <row r="59" spans="2:17" ht="60" customHeight="1">
       <c r="B59" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9"/>
     </row>
     <row r="60" spans="2:17" ht="59.5" customHeight="1">
       <c r="B60" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="7"/>
-      <c r="N60" s="7"/>
-      <c r="O60" s="7"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="7"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="M12:Q12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="M13:Q13"/>
+    <mergeCell ref="C60:G60"/>
+    <mergeCell ref="H60:L60"/>
+    <mergeCell ref="M60:Q60"/>
+    <mergeCell ref="C58:G58"/>
+    <mergeCell ref="H58:L58"/>
+    <mergeCell ref="M58:Q58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="H59:L59"/>
+    <mergeCell ref="M59:Q59"/>
+    <mergeCell ref="B54:Q54"/>
+    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="H56:Q56"/>
+    <mergeCell ref="C57:G57"/>
+    <mergeCell ref="H57:L57"/>
+    <mergeCell ref="M57:Q57"/>
+    <mergeCell ref="P48:P50"/>
+    <mergeCell ref="Q48:Q50"/>
+    <mergeCell ref="B52:Q52"/>
+    <mergeCell ref="C53:L53"/>
+    <mergeCell ref="N53:Q53"/>
     <mergeCell ref="B10:Q10"/>
     <mergeCell ref="P3:P5"/>
     <mergeCell ref="Q3:Q5"/>
@@ -1950,27 +1966,15 @@
     <mergeCell ref="N8:Q8"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="H11:Q11"/>
-    <mergeCell ref="P48:P50"/>
-    <mergeCell ref="Q48:Q50"/>
-    <mergeCell ref="B52:Q52"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="N53:Q53"/>
-    <mergeCell ref="B54:Q54"/>
-    <mergeCell ref="B55:Q55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="H56:Q56"/>
-    <mergeCell ref="C57:G57"/>
-    <mergeCell ref="H57:L57"/>
-    <mergeCell ref="M57:Q57"/>
-    <mergeCell ref="C60:G60"/>
-    <mergeCell ref="H60:L60"/>
-    <mergeCell ref="M60:Q60"/>
-    <mergeCell ref="C58:G58"/>
-    <mergeCell ref="H58:L58"/>
-    <mergeCell ref="M58:Q58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="H59:L59"/>
-    <mergeCell ref="M59:Q59"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="M12:Q12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="M13:Q13"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2003,16 +2007,16 @@
       </c>
     </row>
     <row r="6" spans="2:17">
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
     </row>
     <row r="7" spans="2:17">
-      <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
     </row>
     <row r="8" spans="2:17">
-      <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
     </row>
     <row r="9" spans="2:17">
       <c r="P9" s="5"/>
@@ -2042,67 +2046,67 @@
       <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
       <c r="M11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="10"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="8"/>
     </row>
     <row r="12" spans="2:17" ht="128" customHeight="1">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="13"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="21"/>
     </row>
     <row r="13" spans="2:17" ht="17" customHeight="1">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="16"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:17" ht="26" customHeight="1">
       <c r="B14" s="23" t="s">
@@ -2130,302 +2134,270 @@
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17" t="s">
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
     </row>
     <row r="16" spans="2:17" ht="35.5" customHeight="1">
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
     </row>
     <row r="17" spans="2:17" ht="35.5" customHeight="1">
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
     </row>
     <row r="18" spans="2:17" ht="35.5" customHeight="1">
       <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
     </row>
     <row r="19" spans="2:17" ht="35.5" customHeight="1">
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="2:17" ht="35.5" customHeight="1">
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
     </row>
     <row r="21" spans="2:17" ht="35.5" customHeight="1">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
     </row>
     <row r="22" spans="2:17" ht="35.5" customHeight="1">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
     </row>
     <row r="23" spans="2:17" ht="35.5" customHeight="1">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
     </row>
     <row r="24" spans="2:17" ht="35.5" customHeight="1">
       <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
     </row>
     <row r="25" spans="2:17" ht="35.5" customHeight="1">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
     </row>
     <row r="26" spans="2:17" ht="35.5" customHeight="1">
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
     </row>
     <row r="27" spans="2:17" ht="35.5" customHeight="1">
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="B13:Q13"/>
-    <mergeCell ref="B12:Q12"/>
-    <mergeCell ref="B10:Q10"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="H14:Q14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:L15"/>
-    <mergeCell ref="M15:Q15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:L16"/>
-    <mergeCell ref="M16:Q16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="M17:Q17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:L18"/>
-    <mergeCell ref="M18:Q18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="M19:Q19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:Q20"/>
-    <mergeCell ref="M24:Q24"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="M21:Q21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:L22"/>
-    <mergeCell ref="M22:Q22"/>
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="H27:L27"/>
     <mergeCell ref="M27:Q27"/>
@@ -2442,6 +2414,38 @@
     <mergeCell ref="M23:Q23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="H24:L24"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:Q20"/>
+    <mergeCell ref="M24:Q24"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="M21:Q21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="M22:Q22"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="M18:Q18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="M19:Q19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:L16"/>
+    <mergeCell ref="M16:Q16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:L17"/>
+    <mergeCell ref="M17:Q17"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="H14:Q14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:L15"/>
+    <mergeCell ref="M15:Q15"/>
+    <mergeCell ref="B13:Q13"/>
+    <mergeCell ref="B12:Q12"/>
+    <mergeCell ref="B10:Q10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="N11:Q11"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
